--- a/4_week_report.xlsx
+++ b/4_week_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>463.6</v>
+        <v>461.2</v>
       </c>
       <c r="D3" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E3" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="F3" t="n">
-        <v>508</v>
+        <v>560</v>
       </c>
       <c r="G3" t="n">
-        <v>629</v>
+        <v>792</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -567,10 +567,10 @@
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.28</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
         <v>12</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>506</v>
+        <v>518.2</v>
       </c>
       <c r="D9" t="n">
-        <v>469</v>
+        <v>424</v>
       </c>
       <c r="E9" t="n">
-        <v>571</v>
+        <v>513</v>
       </c>
       <c r="F9" t="n">
-        <v>695</v>
+        <v>662</v>
       </c>
       <c r="G9" t="n">
-        <v>890</v>
+        <v>912</v>
       </c>
     </row>
     <row r="10">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>155.88</v>
+        <v>198.66</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="E10" t="n">
-        <v>253</v>
+        <v>376</v>
       </c>
       <c r="F10" t="n">
-        <v>292</v>
+        <v>443</v>
       </c>
       <c r="G10" t="n">
-        <v>349</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.2</v>
+        <v>32.1</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>522.6</v>
+        <v>730.6</v>
       </c>
       <c r="D14" t="n">
-        <v>470</v>
+        <v>562</v>
       </c>
       <c r="E14" t="n">
-        <v>565</v>
+        <v>674</v>
       </c>
       <c r="F14" t="n">
-        <v>667</v>
+        <v>803</v>
       </c>
       <c r="G14" t="n">
-        <v>824</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="15">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="n">
-        <v>11</v>
-      </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -867,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -888,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100.1</v>
+        <v>80.60000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G18" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19">
@@ -948,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>547</v>
+        <v>631</v>
       </c>
       <c r="D20" t="n">
-        <v>522</v>
+        <v>639</v>
       </c>
       <c r="E20" t="n">
-        <v>591</v>
+        <v>743</v>
       </c>
       <c r="F20" t="n">
-        <v>646</v>
+        <v>836</v>
       </c>
       <c r="G20" t="n">
-        <v>728</v>
+        <v>981</v>
       </c>
     </row>
     <row r="21">
@@ -990,19 +990,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.56</v>
+        <v>32.44</v>
       </c>
       <c r="D22" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="E22" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="F22" t="n">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="G22" t="n">
-        <v>448</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23">
@@ -1050,13 +1050,13 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>921</v>
+        <v>980.2</v>
       </c>
       <c r="D24" t="n">
-        <v>902</v>
+        <v>861</v>
       </c>
       <c r="E24" t="n">
-        <v>1070</v>
+        <v>1006</v>
       </c>
       <c r="F24" t="n">
-        <v>1234</v>
+        <v>1135</v>
       </c>
       <c r="G24" t="n">
-        <v>1487</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="25">
@@ -1110,7 +1110,7 @@
         <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1134,7 +1134,7 @@
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
         <v>26</v>
@@ -1152,19 +1152,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>674.4000000000001</v>
+        <v>505</v>
       </c>
       <c r="D27" t="n">
-        <v>666</v>
+        <v>467</v>
       </c>
       <c r="E27" t="n">
-        <v>808</v>
+        <v>564</v>
       </c>
       <c r="F27" t="n">
-        <v>980</v>
+        <v>674</v>
       </c>
       <c r="G27" t="n">
-        <v>1257</v>
+        <v>848</v>
       </c>
     </row>
     <row r="28">
@@ -1179,19 +1179,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>231.4</v>
+        <v>212</v>
       </c>
       <c r="D28" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F28" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G28" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29">
@@ -1233,19 +1233,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.240000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
@@ -1260,19 +1260,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.380000000000001</v>
+        <v>5.160000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>854</v>
+        <v>707.1</v>
       </c>
       <c r="D32" t="n">
-        <v>795</v>
+        <v>641</v>
       </c>
       <c r="E32" t="n">
-        <v>897</v>
+        <v>765</v>
       </c>
       <c r="F32" t="n">
-        <v>981</v>
+        <v>891</v>
       </c>
       <c r="G32" t="n">
-        <v>1103</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="33">
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
         <v>4</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>124.62</v>
+        <v>146.98</v>
       </c>
       <c r="D34" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="E34" t="n">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="F34" t="n">
-        <v>192</v>
+        <v>315</v>
       </c>
       <c r="G34" t="n">
-        <v>233</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5.080000000000001</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
@@ -1404,10 +1404,10 @@
         <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G36" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -1449,19 +1449,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
         <v>7</v>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
@@ -1476,19 +1476,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12.42</v>
+        <v>12.08</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G39" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -1503,19 +1503,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>702.7400000000002</v>
+        <v>611.6400000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>929</v>
+        <v>751</v>
       </c>
       <c r="E40" t="n">
-        <v>1118</v>
+        <v>910</v>
       </c>
       <c r="F40" t="n">
-        <v>1322</v>
+        <v>1096</v>
       </c>
       <c r="G40" t="n">
-        <v>1641</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="41">
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -1584,19 +1584,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E43" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F43" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="G43" t="n">
-        <v>167</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44">
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.68</v>
+        <v>3.94</v>
       </c>
       <c r="D44" t="n">
         <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G44" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45">
@@ -1638,19 +1638,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17.2</v>
+        <v>8.100000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E45" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F45" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G45" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="D46" t="n">
-        <v>458</v>
+        <v>542</v>
       </c>
       <c r="E46" t="n">
-        <v>522</v>
+        <v>633</v>
       </c>
       <c r="F46" t="n">
-        <v>576</v>
+        <v>719</v>
       </c>
       <c r="G46" t="n">
-        <v>656</v>
+        <v>851</v>
       </c>
     </row>
     <row r="47">
@@ -1698,13 +1698,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="D48" t="n">
         <v>4</v>
@@ -1746,19 +1746,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>160.3</v>
+        <v>308.1</v>
       </c>
       <c r="D49" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E49" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F49" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G49" t="n">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50">
@@ -1773,19 +1773,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>844</v>
+        <v>1288.6</v>
       </c>
       <c r="D50" t="n">
-        <v>690</v>
+        <v>1233</v>
       </c>
       <c r="E50" t="n">
-        <v>832</v>
+        <v>1485</v>
       </c>
       <c r="F50" t="n">
-        <v>986</v>
+        <v>1777</v>
       </c>
       <c r="G50" t="n">
-        <v>1224</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="51">
@@ -1800,19 +1800,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>192.4</v>
+        <v>246</v>
       </c>
       <c r="D51" t="n">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="E51" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="F51" t="n">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="G51" t="n">
-        <v>263</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52">
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -1854,19 +1854,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>62</v>
+        <v>76.70000000000002</v>
       </c>
       <c r="D53" t="n">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="E53" t="n">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="F53" t="n">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="G53" t="n">
-        <v>117</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54">
@@ -1881,19 +1881,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.140000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="D54" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G54" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
         <v>4</v>
@@ -1920,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
@@ -1935,19 +1935,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16.92</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
+        <v>18</v>
+      </c>
+      <c r="G56" t="n">
         <v>26</v>
-      </c>
-      <c r="G56" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -1971,7 +1971,7 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>12</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>177.98</v>
+        <v>120.98</v>
       </c>
       <c r="D58" t="n">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="E58" t="n">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="F58" t="n">
-        <v>272</v>
+        <v>374</v>
       </c>
       <c r="G58" t="n">
-        <v>353</v>
+        <v>534</v>
       </c>
     </row>
     <row r="59">
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>91</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E59" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F59" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G59" t="n">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60">
@@ -2043,19 +2043,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10.14</v>
+        <v>18.28</v>
       </c>
       <c r="D60" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E60" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F60" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G60" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61">
@@ -2070,19 +2070,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5.74</v>
+        <v>12.18</v>
       </c>
       <c r="D61" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E61" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F61" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G61" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62">
@@ -2097,19 +2097,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>455</v>
+        <v>593.1</v>
       </c>
       <c r="D62" t="n">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="E62" t="n">
-        <v>492</v>
+        <v>585</v>
       </c>
       <c r="F62" t="n">
-        <v>556</v>
+        <v>691</v>
       </c>
       <c r="G62" t="n">
-        <v>654</v>
+        <v>859</v>
       </c>
     </row>
     <row r="63">
@@ -2124,19 +2124,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>52</v>
+        <v>54.7</v>
       </c>
       <c r="D64" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E64" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F64" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G64" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65">
@@ -2178,19 +2178,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.82</v>
+        <v>1.8</v>
       </c>
       <c r="D65" t="n">
         <v>10</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66">
@@ -2205,19 +2205,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>106.6</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D66" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E66" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F66" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G66" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67">
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>19.66</v>
+        <v>17.06</v>
       </c>
       <c r="D67" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E67" t="n">
+        <v>18</v>
+      </c>
+      <c r="F67" t="n">
         <v>34</v>
       </c>
-      <c r="F67" t="n">
-        <v>54</v>
-      </c>
       <c r="G67" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68">
@@ -2259,19 +2259,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.84</v>
+        <v>10.56</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
@@ -2286,19 +2286,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>50.26000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="D69" t="n">
         <v>141</v>
       </c>
       <c r="E69" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F69" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="G69" t="n">
-        <v>292</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70">
@@ -2313,19 +2313,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>68.60000000000001</v>
+        <v>113.9</v>
       </c>
       <c r="D70" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E70" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="F70" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G70" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71">
@@ -2340,19 +2340,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>159</v>
+        <v>149.1</v>
       </c>
       <c r="D71" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E71" t="n">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="F71" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G71" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72">
@@ -2367,19 +2367,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="D72" t="n">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="E72" t="n">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="F72" t="n">
-        <v>332</v>
+        <v>409</v>
       </c>
       <c r="G72" t="n">
-        <v>379</v>
+        <v>477</v>
       </c>
     </row>
     <row r="73">
@@ -2394,19 +2394,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>56.10000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="D73" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F73" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G73" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74">
@@ -2421,19 +2421,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10.76</v>
+        <v>10.32</v>
       </c>
       <c r="D74" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E74" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F74" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G74" t="n">
-        <v>146</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75">
@@ -2448,19 +2448,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>17.28</v>
+        <v>12.04</v>
       </c>
       <c r="D75" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E75" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F75" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G75" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>92</v>
+        <v>51.6</v>
       </c>
       <c r="D76" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E76" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F76" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="G76" t="n">
-        <v>167</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77">
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>376.7</v>
+        <v>328.5</v>
       </c>
       <c r="D77" t="n">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="E77" t="n">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="F77" t="n">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="G77" t="n">
-        <v>543</v>
+        <v>515</v>
       </c>
     </row>
     <row r="78">
@@ -2541,7 +2541,7 @@
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -2556,19 +2556,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>77.31999999999999</v>
+        <v>134.06</v>
       </c>
       <c r="D79" t="n">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="E79" t="n">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="F79" t="n">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="G79" t="n">
-        <v>329</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80">
@@ -2583,19 +2583,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.1</v>
+        <v>10.4</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G80" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81">
@@ -2610,19 +2610,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>32.5</v>
+        <v>21.1</v>
       </c>
       <c r="D81" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E81" t="n">
+        <v>23</v>
+      </c>
+      <c r="F81" t="n">
         <v>30</v>
       </c>
-      <c r="F81" t="n">
-        <v>38</v>
-      </c>
       <c r="G81" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82">
@@ -2637,19 +2637,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
         <v>8</v>
       </c>
-      <c r="E82" t="n">
-        <v>8</v>
-      </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>13</v>
-      </c>
-      <c r="G82" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -2664,19 +2664,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>90.45999999999999</v>
+        <v>110.7</v>
       </c>
       <c r="D83" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E83" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F83" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G83" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1921.4</v>
+        <v>2012.9</v>
       </c>
       <c r="D84" t="n">
-        <v>1478</v>
+        <v>1774</v>
       </c>
       <c r="E84" t="n">
-        <v>1697</v>
+        <v>2071</v>
       </c>
       <c r="F84" t="n">
-        <v>1882</v>
+        <v>2354</v>
       </c>
       <c r="G84" t="n">
-        <v>2158</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="85">
@@ -2718,19 +2718,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>37.8</v>
+        <v>35.40000000000001</v>
       </c>
       <c r="D85" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E85" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F85" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G85" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86">
@@ -2745,19 +2745,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>4</v>
@@ -2781,10 +2781,10 @@
         <v>4</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -2799,19 +2799,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D88" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E88" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F88" t="n">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G88" t="n">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89">
@@ -2826,19 +2826,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>77.80000000000001</v>
+        <v>98.36000000000001</v>
       </c>
       <c r="D89" t="n">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E89" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="F89" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="G89" t="n">
-        <v>312</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
         <v>4</v>
@@ -2880,19 +2880,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>116.28</v>
+        <v>160</v>
       </c>
       <c r="D91" t="n">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="E91" t="n">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="F91" t="n">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="G91" t="n">
-        <v>366</v>
+        <v>287</v>
       </c>
     </row>
     <row r="92">
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>431.6</v>
+        <v>259.84</v>
       </c>
       <c r="D92" t="n">
-        <v>332</v>
+        <v>404</v>
       </c>
       <c r="E92" t="n">
-        <v>405</v>
+        <v>490</v>
       </c>
       <c r="F92" t="n">
-        <v>491</v>
+        <v>631</v>
       </c>
       <c r="G92" t="n">
-        <v>629</v>
+        <v>869</v>
       </c>
     </row>
     <row r="93">
@@ -2946,7 +2946,7 @@
         <v>7</v>
       </c>
       <c r="G93" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -2973,7 +2973,7 @@
         <v>21</v>
       </c>
       <c r="G94" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
@@ -2988,19 +2988,19 @@
         </is>
       </c>
       <c r="C95" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>15</v>
+      </c>
+      <c r="E95" t="n">
+        <v>18</v>
+      </c>
+      <c r="F95" t="n">
         <v>25</v>
       </c>
-      <c r="D95" t="n">
-        <v>20</v>
-      </c>
-      <c r="E95" t="n">
-        <v>27</v>
-      </c>
-      <c r="F95" t="n">
-        <v>32</v>
-      </c>
       <c r="G95" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96">
@@ -3015,19 +3015,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>17.16</v>
+        <v>13.9</v>
       </c>
       <c r="D96" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E96" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F96" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G96" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97">
@@ -3042,19 +3042,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>626.6</v>
+        <v>571.7000000000002</v>
       </c>
       <c r="D97" t="n">
-        <v>506</v>
+        <v>676</v>
       </c>
       <c r="E97" t="n">
-        <v>579</v>
+        <v>802</v>
       </c>
       <c r="F97" t="n">
-        <v>642</v>
+        <v>943</v>
       </c>
       <c r="G97" t="n">
-        <v>734</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="98">
@@ -3069,19 +3069,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>61.90000000000001</v>
+        <v>30.6</v>
       </c>
       <c r="D98" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E98" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F98" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G98" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99">
@@ -3096,19 +3096,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>556.78</v>
+        <v>599.1</v>
       </c>
       <c r="D99" t="n">
-        <v>657</v>
+        <v>711</v>
       </c>
       <c r="E99" t="n">
-        <v>754</v>
+        <v>816</v>
       </c>
       <c r="F99" t="n">
-        <v>836</v>
+        <v>907</v>
       </c>
       <c r="G99" t="n">
-        <v>960</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="100">
@@ -3123,19 +3123,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>214.9</v>
+        <v>357.9000000000001</v>
       </c>
       <c r="D100" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E100" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F100" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G100" t="n">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101">
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>830.3</v>
+        <v>343</v>
       </c>
       <c r="D101" t="n">
-        <v>719</v>
+        <v>490</v>
       </c>
       <c r="E101" t="n">
-        <v>850</v>
+        <v>590</v>
       </c>
       <c r="F101" t="n">
-        <v>974</v>
+        <v>690</v>
       </c>
       <c r="G101" t="n">
-        <v>1163</v>
+        <v>847</v>
       </c>
     </row>
     <row r="102">
@@ -3177,19 +3177,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>458</v>
+        <v>590</v>
       </c>
       <c r="D102" t="n">
-        <v>427</v>
+        <v>595</v>
       </c>
       <c r="E102" t="n">
-        <v>494</v>
+        <v>702</v>
       </c>
       <c r="F102" t="n">
-        <v>552</v>
+        <v>808</v>
       </c>
       <c r="G102" t="n">
-        <v>640</v>
+        <v>971</v>
       </c>
     </row>
     <row r="103">
@@ -3204,19 +3204,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>149.7</v>
+        <v>112.6</v>
       </c>
       <c r="D103" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="E103" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="F103" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="G103" t="n">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104">
@@ -3231,19 +3231,19 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>757.9</v>
+        <v>616.4</v>
       </c>
       <c r="D104" t="n">
-        <v>583</v>
+        <v>475</v>
       </c>
       <c r="E104" t="n">
-        <v>665</v>
+        <v>562</v>
       </c>
       <c r="F104" t="n">
-        <v>734</v>
+        <v>647</v>
       </c>
       <c r="G104" t="n">
-        <v>836</v>
+        <v>776</v>
       </c>
     </row>
     <row r="105">
@@ -3258,19 +3258,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>224.4</v>
+        <v>215.7</v>
       </c>
       <c r="D105" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E105" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F105" t="n">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="G105" t="n">
-        <v>264</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106">
@@ -3285,19 +3285,19 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>143.8</v>
+        <v>157.1</v>
       </c>
       <c r="D106" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E106" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F106" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G106" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107">
@@ -3312,19 +3312,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>464</v>
+        <v>554.9</v>
       </c>
       <c r="D107" t="n">
-        <v>501</v>
+        <v>583</v>
       </c>
       <c r="E107" t="n">
-        <v>565</v>
+        <v>667</v>
       </c>
       <c r="F107" t="n">
-        <v>615</v>
+        <v>740</v>
       </c>
       <c r="G107" t="n">
-        <v>689</v>
+        <v>855</v>
       </c>
     </row>
     <row r="108">
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>134.7</v>
+        <v>129.8</v>
       </c>
       <c r="D108" t="n">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E108" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="F108" t="n">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="G108" t="n">
-        <v>215</v>
+        <v>162</v>
       </c>
     </row>
     <row r="109">
@@ -3393,19 +3393,19 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>240</v>
+        <v>305.2</v>
       </c>
       <c r="D110" t="n">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="E110" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="F110" t="n">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="G110" t="n">
-        <v>468</v>
+        <v>409</v>
       </c>
     </row>
     <row r="111">
@@ -3420,19 +3420,19 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>88.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="D111" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E111" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G111" t="n">
-        <v>145</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
@@ -3447,19 +3447,19 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>108.58</v>
+        <v>60.84</v>
       </c>
       <c r="D112" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="E112" t="n">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="F112" t="n">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="G112" t="n">
-        <v>348</v>
+        <v>481</v>
       </c>
     </row>
     <row r="113">
@@ -3474,19 +3474,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>300.1</v>
+        <v>286</v>
       </c>
       <c r="D113" t="n">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="E113" t="n">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="F113" t="n">
-        <v>298</v>
+        <v>348</v>
       </c>
       <c r="G113" t="n">
-        <v>339</v>
+        <v>404</v>
       </c>
     </row>
     <row r="114">
@@ -3501,19 +3501,19 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>14.08</v>
+        <v>17.7</v>
       </c>
       <c r="D114" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E114" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F114" t="n">
         <v>25</v>
       </c>
       <c r="G114" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>95.2</v>
+        <v>74.82000000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E115" t="n">
         <v>102</v>
       </c>
       <c r="F115" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G115" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="116">
@@ -3555,19 +3555,19 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>26</v>
+        <v>29.5</v>
       </c>
       <c r="D116" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E116" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F116" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G116" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117">
@@ -3582,19 +3582,19 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>13.3</v>
+        <v>11.76</v>
       </c>
       <c r="D117" t="n">
+        <v>16</v>
+      </c>
+      <c r="E117" t="n">
+        <v>20</v>
+      </c>
+      <c r="F117" t="n">
         <v>25</v>
       </c>
-      <c r="E117" t="n">
-        <v>30</v>
-      </c>
-      <c r="F117" t="n">
-        <v>38</v>
-      </c>
       <c r="G117" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118">
@@ -3609,19 +3609,19 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>17.7</v>
+        <v>15.1</v>
       </c>
       <c r="D118" t="n">
+        <v>19</v>
+      </c>
+      <c r="E118" t="n">
+        <v>25</v>
+      </c>
+      <c r="F118" t="n">
         <v>30</v>
       </c>
-      <c r="E118" t="n">
-        <v>38</v>
-      </c>
-      <c r="F118" t="n">
-        <v>47</v>
-      </c>
       <c r="G118" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="119">
@@ -3636,19 +3636,19 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>14.96</v>
+        <v>23.7</v>
       </c>
       <c r="D119" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E119" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F119" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G119" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120">
@@ -3663,19 +3663,19 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>88.10000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="D120" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E120" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F120" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G120" t="n">
-        <v>132</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121">
@@ -3690,19 +3690,19 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E121" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F121" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G121" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122">
@@ -3717,19 +3717,19 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>40.24</v>
+        <v>57.40000000000001</v>
       </c>
       <c r="D122" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E122" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F122" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="G122" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123">
@@ -3744,19 +3744,19 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>14.84</v>
+        <v>16.8</v>
       </c>
       <c r="D123" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E123" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F123" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G123" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="124">
@@ -3771,19 +3771,19 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>64.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="D124" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E124" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F124" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="G124" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
     </row>
     <row r="125">
@@ -3798,19 +3798,19 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>51.98</v>
+        <v>46.12</v>
       </c>
       <c r="D125" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E125" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F125" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="G125" t="n">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126">
@@ -3825,19 +3825,19 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.52</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F126" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G126" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127">
@@ -3879,19 +3879,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>13.04</v>
+        <v>30.14</v>
       </c>
       <c r="D128" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E128" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="F128" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G128" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129">
@@ -3906,19 +3906,19 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>25.46</v>
+        <v>42.40000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E129" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F129" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G129" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="130">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>365.3</v>
+        <v>277.2</v>
       </c>
       <c r="D130" t="n">
-        <v>281</v>
+        <v>396</v>
       </c>
       <c r="E130" t="n">
-        <v>343</v>
+        <v>478</v>
       </c>
       <c r="F130" t="n">
-        <v>420</v>
+        <v>565</v>
       </c>
       <c r="G130" t="n">
-        <v>540</v>
+        <v>702</v>
       </c>
     </row>
     <row r="131">
@@ -3960,19 +3960,19 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>400.4</v>
+        <v>218.4</v>
       </c>
       <c r="D131" t="n">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E131" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F131" t="n">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="G131" t="n">
-        <v>571</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132">
@@ -3987,19 +3987,19 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>161</v>
+        <v>189.88</v>
       </c>
       <c r="D132" t="n">
-        <v>230</v>
+        <v>332</v>
       </c>
       <c r="E132" t="n">
-        <v>280</v>
+        <v>401</v>
       </c>
       <c r="F132" t="n">
-        <v>336</v>
+        <v>475</v>
       </c>
       <c r="G132" t="n">
-        <v>425</v>
+        <v>590</v>
       </c>
     </row>
     <row r="133">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>121.6</v>
+        <v>167.3</v>
       </c>
       <c r="D133" t="n">
-        <v>164</v>
+        <v>239</v>
       </c>
       <c r="E133" t="n">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="F133" t="n">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="G133" t="n">
-        <v>288</v>
+        <v>415</v>
       </c>
     </row>
     <row r="134">
@@ -4041,19 +4041,19 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>82.42000000000002</v>
+        <v>96.5</v>
       </c>
       <c r="D134" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="E134" t="n">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="F134" t="n">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="G134" t="n">
-        <v>314</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135">
@@ -4068,19 +4068,19 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>262.4</v>
+        <v>224.36</v>
       </c>
       <c r="D135" t="n">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="E135" t="n">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="F135" t="n">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="G135" t="n">
-        <v>362</v>
+        <v>462</v>
       </c>
     </row>
     <row r="136">
@@ -4095,19 +4095,19 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>250.6</v>
+        <v>211</v>
       </c>
       <c r="D136" t="n">
-        <v>358</v>
+        <v>235</v>
       </c>
       <c r="E136" t="n">
-        <v>428</v>
+        <v>285</v>
       </c>
       <c r="F136" t="n">
-        <v>501</v>
+        <v>346</v>
       </c>
       <c r="G136" t="n">
-        <v>613</v>
+        <v>445</v>
       </c>
     </row>
     <row r="137">
@@ -4122,19 +4122,19 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>96.14000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D137" t="n">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E137" t="n">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="F137" t="n">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="G137" t="n">
-        <v>235</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138">
@@ -4149,19 +4149,19 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>164.24</v>
+        <v>194.6</v>
       </c>
       <c r="D138" t="n">
-        <v>290</v>
+        <v>237</v>
       </c>
       <c r="E138" t="n">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="F138" t="n">
-        <v>396</v>
+        <v>321</v>
       </c>
       <c r="G138" t="n">
-        <v>476</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139">
@@ -4203,19 +4203,19 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>245.02</v>
+        <v>281.8</v>
       </c>
       <c r="D140" t="n">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="E140" t="n">
-        <v>348</v>
+        <v>280</v>
       </c>
       <c r="F140" t="n">
-        <v>388</v>
+        <v>326</v>
       </c>
       <c r="G140" t="n">
-        <v>448</v>
+        <v>397</v>
       </c>
     </row>
     <row r="141">
@@ -4230,19 +4230,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>14.3</v>
+        <v>9.299999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E141" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F141" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G141" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -4257,19 +4257,19 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>28</v>
+        <v>22.86</v>
       </c>
       <c r="D142" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E142" t="n">
+        <v>38</v>
+      </c>
+      <c r="F142" t="n">
+        <v>50</v>
+      </c>
+      <c r="G142" t="n">
         <v>71</v>
-      </c>
-      <c r="F142" t="n">
-        <v>92</v>
-      </c>
-      <c r="G142" t="n">
-        <v>128</v>
       </c>
     </row>
     <row r="143">
@@ -4284,19 +4284,19 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>30</v>
+        <v>41.26000000000001</v>
       </c>
       <c r="D143" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E143" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F143" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="G143" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
     </row>
     <row r="144">
@@ -4311,19 +4311,19 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>4</v>
+        <v>5.399999999999999</v>
       </c>
       <c r="D144" t="n">
+        <v>9</v>
+      </c>
+      <c r="E144" t="n">
         <v>12</v>
       </c>
-      <c r="E144" t="n">
-        <v>15</v>
-      </c>
       <c r="F144" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G144" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145">
@@ -4338,19 +4338,19 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>48.14</v>
+        <v>45.60000000000001</v>
       </c>
       <c r="D145" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F145" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G145" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="146">
@@ -4365,19 +4365,19 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>21</v>
+        <v>29.9</v>
       </c>
       <c r="D146" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E146" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F146" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G146" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="147">
@@ -4392,19 +4392,19 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>29</v>
+        <v>35.18</v>
       </c>
       <c r="D147" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E147" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F147" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G147" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148">
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D148" t="n">
+        <v>17</v>
+      </c>
+      <c r="E148" t="n">
+        <v>21</v>
+      </c>
+      <c r="F148" t="n">
         <v>25</v>
       </c>
-      <c r="E148" t="n">
-        <v>32</v>
-      </c>
-      <c r="F148" t="n">
-        <v>38</v>
-      </c>
       <c r="G148" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149">
@@ -4446,19 +4446,19 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D149" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E149" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F149" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G149" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="150">
@@ -4476,16 +4476,16 @@
         <v>8</v>
       </c>
       <c r="D150" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E150" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F150" t="n">
+        <v>13</v>
+      </c>
+      <c r="G150" t="n">
         <v>17</v>
-      </c>
-      <c r="G150" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="151">
@@ -4500,19 +4500,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D151" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E151" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F151" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="G151" t="n">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="152">
@@ -4527,19 +4527,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E152" t="n">
         <v>8</v>
       </c>
       <c r="F152" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G152" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153">
@@ -4554,64 +4554,64 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>455</v>
+        <v>711</v>
       </c>
       <c r="D153" t="n">
-        <v>627</v>
+        <v>991</v>
       </c>
       <c r="E153" t="n">
-        <v>747</v>
+        <v>1194</v>
       </c>
       <c r="F153" t="n">
-        <v>868</v>
+        <v>1509</v>
       </c>
       <c r="G153" t="n">
-        <v>1055</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B0F3QD6QQL</t>
+          <t>B083Y27ZG7</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>H610M S2H V2</t>
+          <t>H810M GAMING WIFI6</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>252</v>
+        <v>7.600000000000001</v>
       </c>
       <c r="D154" t="n">
-        <v>255</v>
+        <v>14</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>B0F3PT2QVZ</t>
+          <t>B0F3PQWDP8</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>H810M S2H</t>
+          <t>W790 AI TOP</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4620,33 +4620,6 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0F3PQWDP8</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>W790 AI TOP</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>4</v>
-      </c>
-      <c r="D156" t="n">
-        <v>4</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
         <v>0</v>
       </c>
     </row>
